--- a/Client/Bin/Resources/Data/xlsx/DT_StaticLevel.xlsx
+++ b/Client/Bin/Resources/Data/xlsx/DT_StaticLevel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\Desktop\Jusin\GitDesktop\Dx11_Naruto\Client\Bin\Resources\Data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E68FF24-035B-4859-980F-97876F561C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F03744-43ED-4ADA-B8FA-35AECCFA8258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C433F76E-8025-441F-9A39-EF75013F3277}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
-  <si>
-    <t>Type</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -40,28 +37,16 @@
     <t>Extra</t>
   </si>
   <si>
-    <t>Texture</t>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_TEXTURE_DEFAULT</t>
   </si>
   <si>
     <t>Static</t>
   </si>
   <si>
-    <t>CombatStat</t>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_COMBAT_STAT</t>
   </si>
   <si>
-    <t>Buffer_Rect</t>
-  </si>
-  <si>
     <t>COMPONENT_TYPE_RECT</t>
-  </si>
-  <si>
-    <t>Shader</t>
   </si>
   <si>
     <t>COMPONENT_TYPE_SHADER</t>
@@ -1019,10 +1004,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BE75A2-C6A6-40F5-BD93-79C675EA994D}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.375" customWidth="1"/>
+    <col min="2" max="2" width="48.375" customWidth="1"/>
+    <col min="3" max="3" width="49.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1038,61 +1028,46 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
+      <c r="D4" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D5" t="s">
         <v>10</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
